--- a/docs/formacao/enfermagem-geral-nov-a/Cronograma-Enfermagem-Geral-III-Modulo-NOV-A.xlsx
+++ b/docs/formacao/enfermagem-geral-nov-a/Cronograma-Enfermagem-Geral-III-Modulo-NOV-A.xlsx
@@ -10,9 +10,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cronograma" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verificação" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Seminários" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sábados" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estágios e defesa" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Financeiro" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cronograma'!$A$2:$L$250</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sábados'!$A$2:$J$98</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -24,7 +28,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,8 +75,14 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Cambria"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -129,6 +139,16 @@
         <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4DDF4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEAF4"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -156,7 +176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -289,6 +309,51 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6794,7 +6859,7 @@
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>05/01/2027</t>
+          <t>22/12/2026</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
@@ -6850,7 +6915,7 @@
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>05/01/2027</t>
+          <t>22/12/2026</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
@@ -6906,7 +6971,7 @@
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>05/01/2027</t>
+          <t>22/12/2026</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
@@ -6962,7 +7027,7 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>05/01/2027</t>
+          <t>22/12/2026</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
@@ -15881,4 +15946,5542 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J102"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="62" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gestão de Enfermagem e Projecto Tecnológico — 24 sábados, 05/12/2026 a 29/05/2027, 180 h · Prof. Santos Salote</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>N.º</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Dia</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Horário</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Bloco</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Disciplina</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Unidade temática</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Tema da sessão</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Duração (min)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="49" t="inlineStr">
+        <is>
+          <t>05/12/2026</t>
+        </is>
+      </c>
+      <c r="C3" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D3" s="49" t="inlineStr">
+        <is>
+          <t>08h00–10h00</t>
+        </is>
+      </c>
+      <c r="E3" s="49" t="inlineStr">
+        <is>
+          <t>1.º tempo</t>
+        </is>
+      </c>
+      <c r="F3" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G3" s="51" t="inlineStr">
+        <is>
+          <t>UI — Fundamentos da gestão em enfermagem</t>
+        </is>
+      </c>
+      <c r="H3" s="51" t="inlineStr">
+        <is>
+          <t>Apresentação da disciplina; funções de gestão em enfermagem e âmbito do Técnico de Enfermagem</t>
+        </is>
+      </c>
+      <c r="I3" s="48" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="J3" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>05/12/2026</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>10h00–10h30</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Intervalo</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>Intervalo regulamentar</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="49" t="inlineStr">
+        <is>
+          <t>05/12/2026</t>
+        </is>
+      </c>
+      <c r="C5" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D5" s="49" t="inlineStr">
+        <is>
+          <t>10h30–12h30</t>
+        </is>
+      </c>
+      <c r="E5" s="49" t="inlineStr">
+        <is>
+          <t>2.º tempo</t>
+        </is>
+      </c>
+      <c r="F5" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G5" s="51" t="inlineStr">
+        <is>
+          <t>UI — Fundamentos da gestão em enfermagem</t>
+        </is>
+      </c>
+      <c r="H5" s="51" t="inlineStr">
+        <is>
+          <t>Apresentação da disciplina; funções de gestão em enfermagem e âmbito do Técnico de Enfermagem</t>
+        </is>
+      </c>
+      <c r="I5" s="48" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="J5" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="52" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="53" t="inlineStr">
+        <is>
+          <t>05/12/2026</t>
+        </is>
+      </c>
+      <c r="C6" s="53" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D6" s="53" t="inlineStr">
+        <is>
+          <t>12h30–16h00</t>
+        </is>
+      </c>
+      <c r="E6" s="53" t="inlineStr">
+        <is>
+          <t>Bloco de projecto</t>
+        </is>
+      </c>
+      <c r="F6" s="54" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="G6" s="55" t="inlineStr">
+        <is>
+          <t>UI — Enquadramento do trabalho de fim de curso</t>
+        </is>
+      </c>
+      <c r="H6" s="55" t="inlineStr">
+        <is>
+          <t>O trabalho de fim de curso: natureza, tipos, critérios de avaliação e calendário</t>
+        </is>
+      </c>
+      <c r="I6" s="52" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="J6" s="52" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="49" t="inlineStr">
+        <is>
+          <t>12/12/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D7" s="49" t="inlineStr">
+        <is>
+          <t>08h00–10h00</t>
+        </is>
+      </c>
+      <c r="E7" s="49" t="inlineStr">
+        <is>
+          <t>1.º tempo</t>
+        </is>
+      </c>
+      <c r="F7" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G7" s="51" t="inlineStr">
+        <is>
+          <t>UI — Fundamentos da gestão em enfermagem</t>
+        </is>
+      </c>
+      <c r="H7" s="51" t="inlineStr">
+        <is>
+          <t>Organização do serviço de enfermagem: estrutura, cadeia hierárquica e circuitos internos</t>
+        </is>
+      </c>
+      <c r="I7" s="48" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="J7" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>12/12/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>10h00–10h30</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Intervalo</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Intervalo regulamentar</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="48" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="49" t="inlineStr">
+        <is>
+          <t>12/12/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D9" s="49" t="inlineStr">
+        <is>
+          <t>10h30–12h30</t>
+        </is>
+      </c>
+      <c r="E9" s="49" t="inlineStr">
+        <is>
+          <t>2.º tempo</t>
+        </is>
+      </c>
+      <c r="F9" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G9" s="51" t="inlineStr">
+        <is>
+          <t>UI — Fundamentos da gestão em enfermagem</t>
+        </is>
+      </c>
+      <c r="H9" s="51" t="inlineStr">
+        <is>
+          <t>Organização do serviço de enfermagem: estrutura, cadeia hierárquica e circuitos internos</t>
+        </is>
+      </c>
+      <c r="I9" s="48" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="J9" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="52" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="53" t="inlineStr">
+        <is>
+          <t>12/12/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="53" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D10" s="53" t="inlineStr">
+        <is>
+          <t>12h30–16h00</t>
+        </is>
+      </c>
+      <c r="E10" s="53" t="inlineStr">
+        <is>
+          <t>Bloco de projecto</t>
+        </is>
+      </c>
+      <c r="F10" s="54" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="G10" s="55" t="inlineStr">
+        <is>
+          <t>UI — Enquadramento do trabalho de fim de curso</t>
+        </is>
+      </c>
+      <c r="H10" s="55" t="inlineStr">
+        <is>
+          <t>Constituição dos grupos, atribuição do tutor e regras de funcionamento</t>
+        </is>
+      </c>
+      <c r="I10" s="52" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="J10" s="52" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="48" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="49" t="inlineStr">
+        <is>
+          <t>19/12/2026</t>
+        </is>
+      </c>
+      <c r="C11" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D11" s="49" t="inlineStr">
+        <is>
+          <t>08h00–10h00</t>
+        </is>
+      </c>
+      <c r="E11" s="49" t="inlineStr">
+        <is>
+          <t>1.º tempo</t>
+        </is>
+      </c>
+      <c r="F11" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G11" s="51" t="inlineStr">
+        <is>
+          <t>UI — Fundamentos da gestão em enfermagem</t>
+        </is>
+      </c>
+      <c r="H11" s="51" t="inlineStr">
+        <is>
+          <t>Liderança e estilos de chefia; o papel do chefe de equipa de turno</t>
+        </is>
+      </c>
+      <c r="I11" s="48" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="J11" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>19/12/2026</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>10h00–10h30</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>Intervalo</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>Intervalo regulamentar</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="48" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="49" t="inlineStr">
+        <is>
+          <t>19/12/2026</t>
+        </is>
+      </c>
+      <c r="C13" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D13" s="49" t="inlineStr">
+        <is>
+          <t>10h30–12h30</t>
+        </is>
+      </c>
+      <c r="E13" s="49" t="inlineStr">
+        <is>
+          <t>2.º tempo</t>
+        </is>
+      </c>
+      <c r="F13" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G13" s="51" t="inlineStr">
+        <is>
+          <t>UI — Fundamentos da gestão em enfermagem</t>
+        </is>
+      </c>
+      <c r="H13" s="51" t="inlineStr">
+        <is>
+          <t>Liderança e estilos de chefia; o papel do chefe de equipa de turno</t>
+        </is>
+      </c>
+      <c r="I13" s="48" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="J13" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="52" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="53" t="inlineStr">
+        <is>
+          <t>19/12/2026</t>
+        </is>
+      </c>
+      <c r="C14" s="53" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D14" s="53" t="inlineStr">
+        <is>
+          <t>12h30–16h00</t>
+        </is>
+      </c>
+      <c r="E14" s="53" t="inlineStr">
+        <is>
+          <t>Bloco de projecto</t>
+        </is>
+      </c>
+      <c r="F14" s="54" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="G14" s="55" t="inlineStr">
+        <is>
+          <t>UI — Enquadramento do trabalho de fim de curso</t>
+        </is>
+      </c>
+      <c r="H14" s="55" t="inlineStr">
+        <is>
+          <t>Escolha do tema: critérios de relevância, exequibilidade e pertinência clínica</t>
+        </is>
+      </c>
+      <c r="I14" s="52" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="J14" s="52" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="48" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="49" t="inlineStr">
+        <is>
+          <t>09/01/2027</t>
+        </is>
+      </c>
+      <c r="C15" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D15" s="49" t="inlineStr">
+        <is>
+          <t>08h00–10h00</t>
+        </is>
+      </c>
+      <c r="E15" s="49" t="inlineStr">
+        <is>
+          <t>1.º tempo</t>
+        </is>
+      </c>
+      <c r="F15" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G15" s="51" t="inlineStr">
+        <is>
+          <t>UII — Gestão de recursos humanos</t>
+        </is>
+      </c>
+      <c r="H15" s="51" t="inlineStr">
+        <is>
+          <t>Planeamento do trabalho de enfermagem: métodos de distribuição de doentes pela equipa</t>
+        </is>
+      </c>
+      <c r="I15" s="48" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="J15" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>09/01/2027</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>10h00–10h30</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>Intervalo</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>Intervalo regulamentar</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="48" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="49" t="inlineStr">
+        <is>
+          <t>09/01/2027</t>
+        </is>
+      </c>
+      <c r="C17" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D17" s="49" t="inlineStr">
+        <is>
+          <t>10h30–12h30</t>
+        </is>
+      </c>
+      <c r="E17" s="49" t="inlineStr">
+        <is>
+          <t>2.º tempo</t>
+        </is>
+      </c>
+      <c r="F17" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G17" s="51" t="inlineStr">
+        <is>
+          <t>UII — Gestão de recursos humanos</t>
+        </is>
+      </c>
+      <c r="H17" s="51" t="inlineStr">
+        <is>
+          <t>Planeamento do trabalho de enfermagem: métodos de distribuição de doentes pela equipa</t>
+        </is>
+      </c>
+      <c r="I17" s="48" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="J17" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="52" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="53" t="inlineStr">
+        <is>
+          <t>09/01/2027</t>
+        </is>
+      </c>
+      <c r="C18" s="53" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D18" s="53" t="inlineStr">
+        <is>
+          <t>12h30–16h00</t>
+        </is>
+      </c>
+      <c r="E18" s="53" t="inlineStr">
+        <is>
+          <t>Bloco de projecto</t>
+        </is>
+      </c>
+      <c r="F18" s="54" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="G18" s="55" t="inlineStr">
+        <is>
+          <t>UII — Problema, objectivos e projecto</t>
+        </is>
+      </c>
+      <c r="H18" s="55" t="inlineStr">
+        <is>
+          <t>Formulação do problema, da pergunta de partida e dos objectivos</t>
+        </is>
+      </c>
+      <c r="I18" s="52" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="J18" s="52" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="48" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="49" t="inlineStr">
+        <is>
+          <t>16/01/2027</t>
+        </is>
+      </c>
+      <c r="C19" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D19" s="49" t="inlineStr">
+        <is>
+          <t>08h00–10h00</t>
+        </is>
+      </c>
+      <c r="E19" s="49" t="inlineStr">
+        <is>
+          <t>1.º tempo</t>
+        </is>
+      </c>
+      <c r="F19" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G19" s="51" t="inlineStr">
+        <is>
+          <t>UII — Gestão de recursos humanos</t>
+        </is>
+      </c>
+      <c r="H19" s="51" t="inlineStr">
+        <is>
+          <t>Escalas de serviço: elaboração, rotatividade e cobertura de turnos</t>
+        </is>
+      </c>
+      <c r="I19" s="48" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J19" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>16/01/2027</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>10h00–10h30</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>Intervalo</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>Intervalo regulamentar</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="48" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="49" t="inlineStr">
+        <is>
+          <t>16/01/2027</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D21" s="49" t="inlineStr">
+        <is>
+          <t>10h30–12h30</t>
+        </is>
+      </c>
+      <c r="E21" s="49" t="inlineStr">
+        <is>
+          <t>2.º tempo</t>
+        </is>
+      </c>
+      <c r="F21" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G21" s="51" t="inlineStr">
+        <is>
+          <t>UII — Gestão de recursos humanos</t>
+        </is>
+      </c>
+      <c r="H21" s="51" t="inlineStr">
+        <is>
+          <t>Escalas de serviço: elaboração, rotatividade e cobertura de turnos</t>
+        </is>
+      </c>
+      <c r="I21" s="48" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J21" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="52" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="53" t="inlineStr">
+        <is>
+          <t>16/01/2027</t>
+        </is>
+      </c>
+      <c r="C22" s="53" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D22" s="53" t="inlineStr">
+        <is>
+          <t>12h30–16h00</t>
+        </is>
+      </c>
+      <c r="E22" s="53" t="inlineStr">
+        <is>
+          <t>Bloco de projecto</t>
+        </is>
+      </c>
+      <c r="F22" s="54" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="G22" s="55" t="inlineStr">
+        <is>
+          <t>UII — Problema, objectivos e projecto</t>
+        </is>
+      </c>
+      <c r="H22" s="55" t="inlineStr">
+        <is>
+          <t>Pesquisa bibliográfica: fontes, selecção e leitura crítica</t>
+        </is>
+      </c>
+      <c r="I22" s="52" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J22" s="52" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="48" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="49" t="inlineStr">
+        <is>
+          <t>23/01/2027</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D23" s="49" t="inlineStr">
+        <is>
+          <t>08h00–10h00</t>
+        </is>
+      </c>
+      <c r="E23" s="49" t="inlineStr">
+        <is>
+          <t>1.º tempo</t>
+        </is>
+      </c>
+      <c r="F23" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G23" s="51" t="inlineStr">
+        <is>
+          <t>UII — Gestão de recursos humanos</t>
+        </is>
+      </c>
+      <c r="H23" s="51" t="inlineStr">
+        <is>
+          <t>Gestão de faltas, substituições e horas extraordinárias</t>
+        </is>
+      </c>
+      <c r="I23" s="48" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="J23" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>23/01/2027</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>10h00–10h30</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>Intervalo</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>Intervalo regulamentar</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="48" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="49" t="inlineStr">
+        <is>
+          <t>23/01/2027</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D25" s="49" t="inlineStr">
+        <is>
+          <t>10h30–12h30</t>
+        </is>
+      </c>
+      <c r="E25" s="49" t="inlineStr">
+        <is>
+          <t>2.º tempo</t>
+        </is>
+      </c>
+      <c r="F25" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G25" s="51" t="inlineStr">
+        <is>
+          <t>UII — Gestão de recursos humanos</t>
+        </is>
+      </c>
+      <c r="H25" s="51" t="inlineStr">
+        <is>
+          <t>Gestão de faltas, substituições e horas extraordinárias</t>
+        </is>
+      </c>
+      <c r="I25" s="48" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="J25" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="52" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="53" t="inlineStr">
+        <is>
+          <t>23/01/2027</t>
+        </is>
+      </c>
+      <c r="C26" s="53" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D26" s="53" t="inlineStr">
+        <is>
+          <t>12h30–16h00</t>
+        </is>
+      </c>
+      <c r="E26" s="53" t="inlineStr">
+        <is>
+          <t>Bloco de projecto</t>
+        </is>
+      </c>
+      <c r="F26" s="54" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="G26" s="55" t="inlineStr">
+        <is>
+          <t>UII — Problema, objectivos e projecto</t>
+        </is>
+      </c>
+      <c r="H26" s="55" t="inlineStr">
+        <is>
+          <t>Elaboração do projecto: estrutura do trabalho e cronograma de execução</t>
+        </is>
+      </c>
+      <c r="I26" s="52" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J26" s="52" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="48" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="49" t="inlineStr">
+        <is>
+          <t>30/01/2027</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D27" s="49" t="inlineStr">
+        <is>
+          <t>08h00–10h00</t>
+        </is>
+      </c>
+      <c r="E27" s="49" t="inlineStr">
+        <is>
+          <t>1.º tempo</t>
+        </is>
+      </c>
+      <c r="F27" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G27" s="51" t="inlineStr">
+        <is>
+          <t>UII — Gestão de recursos humanos</t>
+        </is>
+      </c>
+      <c r="H27" s="51" t="inlineStr">
+        <is>
+          <t>Delegação e supervisão de tarefas: o que se delega e o que nunca se delega</t>
+        </is>
+      </c>
+      <c r="I27" s="48" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="J27" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>30/01/2027</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>10h00–10h30</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>Intervalo</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>Intervalo regulamentar</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="48" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="49" t="inlineStr">
+        <is>
+          <t>30/01/2027</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D29" s="49" t="inlineStr">
+        <is>
+          <t>10h30–12h30</t>
+        </is>
+      </c>
+      <c r="E29" s="49" t="inlineStr">
+        <is>
+          <t>2.º tempo</t>
+        </is>
+      </c>
+      <c r="F29" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G29" s="51" t="inlineStr">
+        <is>
+          <t>UII — Gestão de recursos humanos</t>
+        </is>
+      </c>
+      <c r="H29" s="51" t="inlineStr">
+        <is>
+          <t>Delegação e supervisão de tarefas: o que se delega e o que nunca se delega</t>
+        </is>
+      </c>
+      <c r="I29" s="48" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="J29" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="52" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="53" t="inlineStr">
+        <is>
+          <t>30/01/2027</t>
+        </is>
+      </c>
+      <c r="C30" s="53" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D30" s="53" t="inlineStr">
+        <is>
+          <t>12h30–16h00</t>
+        </is>
+      </c>
+      <c r="E30" s="53" t="inlineStr">
+        <is>
+          <t>Bloco de projecto</t>
+        </is>
+      </c>
+      <c r="F30" s="54" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="G30" s="55" t="inlineStr">
+        <is>
+          <t>UII — Problema, objectivos e projecto</t>
+        </is>
+      </c>
+      <c r="H30" s="55" t="inlineStr">
+        <is>
+          <t>1.ª pré-defesa — apresentação do tema, do problema e dos objectivos perante júri</t>
+        </is>
+      </c>
+      <c r="I30" s="52" t="inlineStr">
+        <is>
+          <t>Avaliação prática</t>
+        </is>
+      </c>
+      <c r="J30" s="52" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="48" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="49" t="inlineStr">
+        <is>
+          <t>06/02/2027</t>
+        </is>
+      </c>
+      <c r="C31" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D31" s="49" t="inlineStr">
+        <is>
+          <t>08h00–10h00</t>
+        </is>
+      </c>
+      <c r="E31" s="49" t="inlineStr">
+        <is>
+          <t>1.º tempo</t>
+        </is>
+      </c>
+      <c r="F31" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G31" s="51" t="inlineStr">
+        <is>
+          <t>UII — Gestão de recursos humanos</t>
+        </is>
+      </c>
+      <c r="H31" s="51" t="inlineStr">
+        <is>
+          <t>Integração e acompanhamento de novos profissionais e de estagiários</t>
+        </is>
+      </c>
+      <c r="I31" s="48" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="J31" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>06/02/2027</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>10h00–10h30</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>Intervalo</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>Intervalo regulamentar</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="48" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="49" t="inlineStr">
+        <is>
+          <t>06/02/2027</t>
+        </is>
+      </c>
+      <c r="C33" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D33" s="49" t="inlineStr">
+        <is>
+          <t>10h30–12h30</t>
+        </is>
+      </c>
+      <c r="E33" s="49" t="inlineStr">
+        <is>
+          <t>2.º tempo</t>
+        </is>
+      </c>
+      <c r="F33" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G33" s="51" t="inlineStr">
+        <is>
+          <t>UII — Gestão de recursos humanos</t>
+        </is>
+      </c>
+      <c r="H33" s="51" t="inlineStr">
+        <is>
+          <t>Integração e acompanhamento de novos profissionais e de estagiários</t>
+        </is>
+      </c>
+      <c r="I33" s="48" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="J33" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="52" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="53" t="inlineStr">
+        <is>
+          <t>06/02/2027</t>
+        </is>
+      </c>
+      <c r="C34" s="53" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D34" s="53" t="inlineStr">
+        <is>
+          <t>12h30–16h00</t>
+        </is>
+      </c>
+      <c r="E34" s="53" t="inlineStr">
+        <is>
+          <t>Bloco de projecto</t>
+        </is>
+      </c>
+      <c r="F34" s="54" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="G34" s="55" t="inlineStr">
+        <is>
+          <t>UIII — Metodologia</t>
+        </is>
+      </c>
+      <c r="H34" s="55" t="inlineStr">
+        <is>
+          <t>Metodologia: tipo de estudo, população e amostra</t>
+        </is>
+      </c>
+      <c r="I34" s="52" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="J34" s="52" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="48" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="49" t="inlineStr">
+        <is>
+          <t>13/02/2027</t>
+        </is>
+      </c>
+      <c r="C35" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D35" s="49" t="inlineStr">
+        <is>
+          <t>08h00–10h00</t>
+        </is>
+      </c>
+      <c r="E35" s="49" t="inlineStr">
+        <is>
+          <t>1.º tempo</t>
+        </is>
+      </c>
+      <c r="F35" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G35" s="51" t="inlineStr">
+        <is>
+          <t>UIII — Gestão de recursos materiais</t>
+        </is>
+      </c>
+      <c r="H35" s="51" t="inlineStr">
+        <is>
+          <t>Gestão de recursos materiais: inventário, requisição e reposição do serviço</t>
+        </is>
+      </c>
+      <c r="I35" s="48" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J35" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>13/02/2027</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>10h00–10h30</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>Intervalo</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>Intervalo regulamentar</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J36" s="7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="48" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="49" t="inlineStr">
+        <is>
+          <t>13/02/2027</t>
+        </is>
+      </c>
+      <c r="C37" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D37" s="49" t="inlineStr">
+        <is>
+          <t>10h30–12h30</t>
+        </is>
+      </c>
+      <c r="E37" s="49" t="inlineStr">
+        <is>
+          <t>2.º tempo</t>
+        </is>
+      </c>
+      <c r="F37" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G37" s="51" t="inlineStr">
+        <is>
+          <t>UIII — Gestão de recursos materiais</t>
+        </is>
+      </c>
+      <c r="H37" s="51" t="inlineStr">
+        <is>
+          <t>Gestão de recursos materiais: inventário, requisição e reposição do serviço</t>
+        </is>
+      </c>
+      <c r="I37" s="48" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J37" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="52" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="53" t="inlineStr">
+        <is>
+          <t>13/02/2027</t>
+        </is>
+      </c>
+      <c r="C38" s="53" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D38" s="53" t="inlineStr">
+        <is>
+          <t>12h30–16h00</t>
+        </is>
+      </c>
+      <c r="E38" s="53" t="inlineStr">
+        <is>
+          <t>Bloco de projecto</t>
+        </is>
+      </c>
+      <c r="F38" s="54" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="G38" s="55" t="inlineStr">
+        <is>
+          <t>UIII — Metodologia</t>
+        </is>
+      </c>
+      <c r="H38" s="55" t="inlineStr">
+        <is>
+          <t>Instrumentos de recolha de dados: questionário, entrevista e grelha de observação</t>
+        </is>
+      </c>
+      <c r="I38" s="52" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J38" s="52" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="48" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="49" t="inlineStr">
+        <is>
+          <t>20/02/2027</t>
+        </is>
+      </c>
+      <c r="C39" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D39" s="49" t="inlineStr">
+        <is>
+          <t>08h00–10h00</t>
+        </is>
+      </c>
+      <c r="E39" s="49" t="inlineStr">
+        <is>
+          <t>1.º tempo</t>
+        </is>
+      </c>
+      <c r="F39" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G39" s="51" t="inlineStr">
+        <is>
+          <t>UIII — Gestão de recursos materiais</t>
+        </is>
+      </c>
+      <c r="H39" s="51" t="inlineStr">
+        <is>
+          <t>Farmácia do serviço: armazenamento, controlo de estupefacientes e verificação de validades</t>
+        </is>
+      </c>
+      <c r="I39" s="48" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J39" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>20/02/2027</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>10h00–10h30</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>Intervalo</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>Intervalo regulamentar</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J40" s="7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="48" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="49" t="inlineStr">
+        <is>
+          <t>20/02/2027</t>
+        </is>
+      </c>
+      <c r="C41" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D41" s="49" t="inlineStr">
+        <is>
+          <t>10h30–12h30</t>
+        </is>
+      </c>
+      <c r="E41" s="49" t="inlineStr">
+        <is>
+          <t>2.º tempo</t>
+        </is>
+      </c>
+      <c r="F41" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G41" s="51" t="inlineStr">
+        <is>
+          <t>UIII — Gestão de recursos materiais</t>
+        </is>
+      </c>
+      <c r="H41" s="51" t="inlineStr">
+        <is>
+          <t>Farmácia do serviço: armazenamento, controlo de estupefacientes e verificação de validades</t>
+        </is>
+      </c>
+      <c r="I41" s="48" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J41" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="52" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="53" t="inlineStr">
+        <is>
+          <t>20/02/2027</t>
+        </is>
+      </c>
+      <c r="C42" s="53" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D42" s="53" t="inlineStr">
+        <is>
+          <t>12h30–16h00</t>
+        </is>
+      </c>
+      <c r="E42" s="53" t="inlineStr">
+        <is>
+          <t>Bloco de projecto</t>
+        </is>
+      </c>
+      <c r="F42" s="54" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="G42" s="55" t="inlineStr">
+        <is>
+          <t>UIII — Metodologia</t>
+        </is>
+      </c>
+      <c r="H42" s="55" t="inlineStr">
+        <is>
+          <t>Ética na investigação: consentimento, anonimato e autorização institucional</t>
+        </is>
+      </c>
+      <c r="I42" s="52" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="J42" s="52" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="48" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="49" t="inlineStr">
+        <is>
+          <t>27/02/2027</t>
+        </is>
+      </c>
+      <c r="C43" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D43" s="49" t="inlineStr">
+        <is>
+          <t>08h00–10h00</t>
+        </is>
+      </c>
+      <c r="E43" s="49" t="inlineStr">
+        <is>
+          <t>1.º tempo</t>
+        </is>
+      </c>
+      <c r="F43" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G43" s="51" t="inlineStr">
+        <is>
+          <t>UIII — Gestão de recursos materiais</t>
+        </is>
+      </c>
+      <c r="H43" s="51" t="inlineStr">
+        <is>
+          <t>Cadeia de frio e gestão de vacinas e de hemoderivados no serviço</t>
+        </is>
+      </c>
+      <c r="I43" s="48" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J43" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>27/02/2027</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>10h00–10h30</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>Intervalo</t>
+        </is>
+      </c>
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>Intervalo regulamentar</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J44" s="7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="48" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="49" t="inlineStr">
+        <is>
+          <t>27/02/2027</t>
+        </is>
+      </c>
+      <c r="C45" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D45" s="49" t="inlineStr">
+        <is>
+          <t>10h30–12h30</t>
+        </is>
+      </c>
+      <c r="E45" s="49" t="inlineStr">
+        <is>
+          <t>2.º tempo</t>
+        </is>
+      </c>
+      <c r="F45" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G45" s="51" t="inlineStr">
+        <is>
+          <t>UIII — Gestão de recursos materiais</t>
+        </is>
+      </c>
+      <c r="H45" s="51" t="inlineStr">
+        <is>
+          <t>Cadeia de frio e gestão de vacinas e de hemoderivados no serviço</t>
+        </is>
+      </c>
+      <c r="I45" s="48" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J45" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="52" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="53" t="inlineStr">
+        <is>
+          <t>27/02/2027</t>
+        </is>
+      </c>
+      <c r="C46" s="53" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D46" s="53" t="inlineStr">
+        <is>
+          <t>12h30–16h00</t>
+        </is>
+      </c>
+      <c r="E46" s="53" t="inlineStr">
+        <is>
+          <t>Bloco de projecto</t>
+        </is>
+      </c>
+      <c r="F46" s="54" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="G46" s="55" t="inlineStr">
+        <is>
+          <t>UIII — Metodologia</t>
+        </is>
+      </c>
+      <c r="H46" s="55" t="inlineStr">
+        <is>
+          <t>2.ª pré-defesa — apresentação da metodologia e dos instrumentos perante júri</t>
+        </is>
+      </c>
+      <c r="I46" s="52" t="inlineStr">
+        <is>
+          <t>Avaliação prática</t>
+        </is>
+      </c>
+      <c r="J46" s="52" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="48" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="49" t="inlineStr">
+        <is>
+          <t>06/03/2027</t>
+        </is>
+      </c>
+      <c r="C47" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D47" s="49" t="inlineStr">
+        <is>
+          <t>08h00–10h00</t>
+        </is>
+      </c>
+      <c r="E47" s="49" t="inlineStr">
+        <is>
+          <t>1.º tempo</t>
+        </is>
+      </c>
+      <c r="F47" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G47" s="51" t="inlineStr">
+        <is>
+          <t>UIII — Gestão de recursos materiais</t>
+        </is>
+      </c>
+      <c r="H47" s="51" t="inlineStr">
+        <is>
+          <t>Gestão de resíduos hospitalares e controlo de custos do serviço</t>
+        </is>
+      </c>
+      <c r="I47" s="48" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="J47" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>06/03/2027</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>10h00–10h30</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>Intervalo</t>
+        </is>
+      </c>
+      <c r="F48" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H48" s="10" t="inlineStr">
+        <is>
+          <t>Intervalo regulamentar</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J48" s="7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="49" t="inlineStr">
+        <is>
+          <t>06/03/2027</t>
+        </is>
+      </c>
+      <c r="C49" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D49" s="49" t="inlineStr">
+        <is>
+          <t>10h30–12h30</t>
+        </is>
+      </c>
+      <c r="E49" s="49" t="inlineStr">
+        <is>
+          <t>2.º tempo</t>
+        </is>
+      </c>
+      <c r="F49" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G49" s="51" t="inlineStr">
+        <is>
+          <t>UIII — Gestão de recursos materiais</t>
+        </is>
+      </c>
+      <c r="H49" s="51" t="inlineStr">
+        <is>
+          <t>Gestão de resíduos hospitalares e controlo de custos do serviço</t>
+        </is>
+      </c>
+      <c r="I49" s="48" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="J49" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="52" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="53" t="inlineStr">
+        <is>
+          <t>06/03/2027</t>
+        </is>
+      </c>
+      <c r="C50" s="53" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D50" s="53" t="inlineStr">
+        <is>
+          <t>12h30–16h00</t>
+        </is>
+      </c>
+      <c r="E50" s="53" t="inlineStr">
+        <is>
+          <t>Bloco de projecto</t>
+        </is>
+      </c>
+      <c r="F50" s="54" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="G50" s="55" t="inlineStr">
+        <is>
+          <t>UIV — Recolha e tratamento de dados</t>
+        </is>
+      </c>
+      <c r="H50" s="55" t="inlineStr">
+        <is>
+          <t>Recolha de dados no terreno: organização, registo e controlo de qualidade</t>
+        </is>
+      </c>
+      <c r="I50" s="52" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J50" s="52" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="48" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="49" t="inlineStr">
+        <is>
+          <t>13/03/2027</t>
+        </is>
+      </c>
+      <c r="C51" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D51" s="49" t="inlineStr">
+        <is>
+          <t>08h00–10h00</t>
+        </is>
+      </c>
+      <c r="E51" s="49" t="inlineStr">
+        <is>
+          <t>1.º tempo</t>
+        </is>
+      </c>
+      <c r="F51" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G51" s="51" t="inlineStr">
+        <is>
+          <t>UIV — Qualidade e segurança do doente</t>
+        </is>
+      </c>
+      <c r="H51" s="51" t="inlineStr">
+        <is>
+          <t>Qualidade em saúde: conceitos, indicadores e padrões de cuidados de enfermagem</t>
+        </is>
+      </c>
+      <c r="I51" s="48" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="J51" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>13/03/2027</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>10h00–10h30</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>Intervalo</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G52" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H52" s="10" t="inlineStr">
+        <is>
+          <t>Intervalo regulamentar</t>
+        </is>
+      </c>
+      <c r="I52" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J52" s="7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="48" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="49" t="inlineStr">
+        <is>
+          <t>13/03/2027</t>
+        </is>
+      </c>
+      <c r="C53" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D53" s="49" t="inlineStr">
+        <is>
+          <t>10h30–12h30</t>
+        </is>
+      </c>
+      <c r="E53" s="49" t="inlineStr">
+        <is>
+          <t>2.º tempo</t>
+        </is>
+      </c>
+      <c r="F53" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G53" s="51" t="inlineStr">
+        <is>
+          <t>UIV — Qualidade e segurança do doente</t>
+        </is>
+      </c>
+      <c r="H53" s="51" t="inlineStr">
+        <is>
+          <t>Qualidade em saúde: conceitos, indicadores e padrões de cuidados de enfermagem</t>
+        </is>
+      </c>
+      <c r="I53" s="48" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="J53" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="52" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="53" t="inlineStr">
+        <is>
+          <t>13/03/2027</t>
+        </is>
+      </c>
+      <c r="C54" s="53" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D54" s="53" t="inlineStr">
+        <is>
+          <t>12h30–16h00</t>
+        </is>
+      </c>
+      <c r="E54" s="53" t="inlineStr">
+        <is>
+          <t>Bloco de projecto</t>
+        </is>
+      </c>
+      <c r="F54" s="54" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="G54" s="55" t="inlineStr">
+        <is>
+          <t>UIV — Recolha e tratamento de dados</t>
+        </is>
+      </c>
+      <c r="H54" s="55" t="inlineStr">
+        <is>
+          <t>Tratamento de dados: tabelas, frequências e percentagens</t>
+        </is>
+      </c>
+      <c r="I54" s="52" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J54" s="52" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="48" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="49" t="inlineStr">
+        <is>
+          <t>20/03/2027</t>
+        </is>
+      </c>
+      <c r="C55" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D55" s="49" t="inlineStr">
+        <is>
+          <t>08h00–10h00</t>
+        </is>
+      </c>
+      <c r="E55" s="49" t="inlineStr">
+        <is>
+          <t>1.º tempo</t>
+        </is>
+      </c>
+      <c r="F55" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G55" s="51" t="inlineStr">
+        <is>
+          <t>UIV — Qualidade e segurança do doente</t>
+        </is>
+      </c>
+      <c r="H55" s="51" t="inlineStr">
+        <is>
+          <t>Auditoria interna de enfermagem e listas de verificação de serviço</t>
+        </is>
+      </c>
+      <c r="I55" s="48" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J55" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>20/03/2027</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>10h00–10h30</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>Intervalo</t>
+        </is>
+      </c>
+      <c r="F56" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G56" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H56" s="10" t="inlineStr">
+        <is>
+          <t>Intervalo regulamentar</t>
+        </is>
+      </c>
+      <c r="I56" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J56" s="7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="48" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="49" t="inlineStr">
+        <is>
+          <t>20/03/2027</t>
+        </is>
+      </c>
+      <c r="C57" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D57" s="49" t="inlineStr">
+        <is>
+          <t>10h30–12h30</t>
+        </is>
+      </c>
+      <c r="E57" s="49" t="inlineStr">
+        <is>
+          <t>2.º tempo</t>
+        </is>
+      </c>
+      <c r="F57" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G57" s="51" t="inlineStr">
+        <is>
+          <t>UIV — Qualidade e segurança do doente</t>
+        </is>
+      </c>
+      <c r="H57" s="51" t="inlineStr">
+        <is>
+          <t>Auditoria interna de enfermagem e listas de verificação de serviço</t>
+        </is>
+      </c>
+      <c r="I57" s="48" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J57" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="52" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="53" t="inlineStr">
+        <is>
+          <t>20/03/2027</t>
+        </is>
+      </c>
+      <c r="C58" s="53" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D58" s="53" t="inlineStr">
+        <is>
+          <t>12h30–16h00</t>
+        </is>
+      </c>
+      <c r="E58" s="53" t="inlineStr">
+        <is>
+          <t>Bloco de projecto</t>
+        </is>
+      </c>
+      <c r="F58" s="54" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="G58" s="55" t="inlineStr">
+        <is>
+          <t>UIV — Recolha e tratamento de dados</t>
+        </is>
+      </c>
+      <c r="H58" s="55" t="inlineStr">
+        <is>
+          <t>Apresentação de dados: construção e leitura de gráficos</t>
+        </is>
+      </c>
+      <c r="I58" s="52" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J58" s="52" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="48" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="49" t="inlineStr">
+        <is>
+          <t>27/03/2027</t>
+        </is>
+      </c>
+      <c r="C59" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D59" s="49" t="inlineStr">
+        <is>
+          <t>08h00–10h00</t>
+        </is>
+      </c>
+      <c r="E59" s="49" t="inlineStr">
+        <is>
+          <t>1.º tempo</t>
+        </is>
+      </c>
+      <c r="F59" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G59" s="51" t="inlineStr">
+        <is>
+          <t>UIV — Qualidade e segurança do doente</t>
+        </is>
+      </c>
+      <c r="H59" s="51" t="inlineStr">
+        <is>
+          <t>Segurança do doente: notificação de incidentes e cultura não punitiva</t>
+        </is>
+      </c>
+      <c r="I59" s="48" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="J59" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>27/03/2027</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t>10h00–10h30</t>
+        </is>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>Intervalo</t>
+        </is>
+      </c>
+      <c r="F60" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G60" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H60" s="10" t="inlineStr">
+        <is>
+          <t>Intervalo regulamentar</t>
+        </is>
+      </c>
+      <c r="I60" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J60" s="7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="48" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="49" t="inlineStr">
+        <is>
+          <t>27/03/2027</t>
+        </is>
+      </c>
+      <c r="C61" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D61" s="49" t="inlineStr">
+        <is>
+          <t>10h30–12h30</t>
+        </is>
+      </c>
+      <c r="E61" s="49" t="inlineStr">
+        <is>
+          <t>2.º tempo</t>
+        </is>
+      </c>
+      <c r="F61" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G61" s="51" t="inlineStr">
+        <is>
+          <t>UIV — Qualidade e segurança do doente</t>
+        </is>
+      </c>
+      <c r="H61" s="51" t="inlineStr">
+        <is>
+          <t>Segurança do doente: notificação de incidentes e cultura não punitiva</t>
+        </is>
+      </c>
+      <c r="I61" s="48" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="J61" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="52" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="53" t="inlineStr">
+        <is>
+          <t>27/03/2027</t>
+        </is>
+      </c>
+      <c r="C62" s="53" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D62" s="53" t="inlineStr">
+        <is>
+          <t>12h30–16h00</t>
+        </is>
+      </c>
+      <c r="E62" s="53" t="inlineStr">
+        <is>
+          <t>Bloco de projecto</t>
+        </is>
+      </c>
+      <c r="F62" s="54" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="G62" s="55" t="inlineStr">
+        <is>
+          <t>UIV — Recolha e tratamento de dados</t>
+        </is>
+      </c>
+      <c r="H62" s="55" t="inlineStr">
+        <is>
+          <t>3.ª pré-defesa — apresentação dos resultados preliminares perante júri</t>
+        </is>
+      </c>
+      <c r="I62" s="52" t="inlineStr">
+        <is>
+          <t>Avaliação prática</t>
+        </is>
+      </c>
+      <c r="J62" s="52" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="48" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="49" t="inlineStr">
+        <is>
+          <t>03/04/2027</t>
+        </is>
+      </c>
+      <c r="C63" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D63" s="49" t="inlineStr">
+        <is>
+          <t>08h00–10h00</t>
+        </is>
+      </c>
+      <c r="E63" s="49" t="inlineStr">
+        <is>
+          <t>1.º tempo</t>
+        </is>
+      </c>
+      <c r="F63" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G63" s="51" t="inlineStr">
+        <is>
+          <t>UIV — Qualidade e segurança do doente</t>
+        </is>
+      </c>
+      <c r="H63" s="51" t="inlineStr">
+        <is>
+          <t>Prevenção e controlo de infecção na perspectiva da gestão do serviço</t>
+        </is>
+      </c>
+      <c r="I63" s="48" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="J63" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>03/04/2027</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>10h00–10h30</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>Intervalo</t>
+        </is>
+      </c>
+      <c r="F64" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G64" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H64" s="10" t="inlineStr">
+        <is>
+          <t>Intervalo regulamentar</t>
+        </is>
+      </c>
+      <c r="I64" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J64" s="7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="48" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="49" t="inlineStr">
+        <is>
+          <t>03/04/2027</t>
+        </is>
+      </c>
+      <c r="C65" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D65" s="49" t="inlineStr">
+        <is>
+          <t>10h30–12h30</t>
+        </is>
+      </c>
+      <c r="E65" s="49" t="inlineStr">
+        <is>
+          <t>2.º tempo</t>
+        </is>
+      </c>
+      <c r="F65" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G65" s="51" t="inlineStr">
+        <is>
+          <t>UIV — Qualidade e segurança do doente</t>
+        </is>
+      </c>
+      <c r="H65" s="51" t="inlineStr">
+        <is>
+          <t>Prevenção e controlo de infecção na perspectiva da gestão do serviço</t>
+        </is>
+      </c>
+      <c r="I65" s="48" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="J65" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="52" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" s="53" t="inlineStr">
+        <is>
+          <t>03/04/2027</t>
+        </is>
+      </c>
+      <c r="C66" s="53" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D66" s="53" t="inlineStr">
+        <is>
+          <t>12h30–16h00</t>
+        </is>
+      </c>
+      <c r="E66" s="53" t="inlineStr">
+        <is>
+          <t>Bloco de projecto</t>
+        </is>
+      </c>
+      <c r="F66" s="54" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="G66" s="55" t="inlineStr">
+        <is>
+          <t>UV — Discussão, conclusões e redacção</t>
+        </is>
+      </c>
+      <c r="H66" s="55" t="inlineStr">
+        <is>
+          <t>Discussão dos resultados: confronto com a literatura consultada</t>
+        </is>
+      </c>
+      <c r="I66" s="52" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="J66" s="52" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="48" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" s="49" t="inlineStr">
+        <is>
+          <t>10/04/2027</t>
+        </is>
+      </c>
+      <c r="C67" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D67" s="49" t="inlineStr">
+        <is>
+          <t>08h00–10h00</t>
+        </is>
+      </c>
+      <c r="E67" s="49" t="inlineStr">
+        <is>
+          <t>1.º tempo</t>
+        </is>
+      </c>
+      <c r="F67" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G67" s="51" t="inlineStr">
+        <is>
+          <t>UV — Ética, deontologia e direitos</t>
+        </is>
+      </c>
+      <c r="H67" s="51" t="inlineStr">
+        <is>
+          <t>Ética e deontologia profissional aplicadas à chefia e à supervisão</t>
+        </is>
+      </c>
+      <c r="I67" s="48" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="J67" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>10/04/2027</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>10h00–10h30</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>Intervalo</t>
+        </is>
+      </c>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G68" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H68" s="10" t="inlineStr">
+        <is>
+          <t>Intervalo regulamentar</t>
+        </is>
+      </c>
+      <c r="I68" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J68" s="7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="48" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" s="49" t="inlineStr">
+        <is>
+          <t>10/04/2027</t>
+        </is>
+      </c>
+      <c r="C69" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D69" s="49" t="inlineStr">
+        <is>
+          <t>10h30–12h30</t>
+        </is>
+      </c>
+      <c r="E69" s="49" t="inlineStr">
+        <is>
+          <t>2.º tempo</t>
+        </is>
+      </c>
+      <c r="F69" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G69" s="51" t="inlineStr">
+        <is>
+          <t>UV — Ética, deontologia e direitos</t>
+        </is>
+      </c>
+      <c r="H69" s="51" t="inlineStr">
+        <is>
+          <t>Ética e deontologia profissional aplicadas à chefia e à supervisão</t>
+        </is>
+      </c>
+      <c r="I69" s="48" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="J69" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="52" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" s="53" t="inlineStr">
+        <is>
+          <t>10/04/2027</t>
+        </is>
+      </c>
+      <c r="C70" s="53" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D70" s="53" t="inlineStr">
+        <is>
+          <t>12h30–16h00</t>
+        </is>
+      </c>
+      <c r="E70" s="53" t="inlineStr">
+        <is>
+          <t>Bloco de projecto</t>
+        </is>
+      </c>
+      <c r="F70" s="54" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="G70" s="55" t="inlineStr">
+        <is>
+          <t>UV — Discussão, conclusões e redacção</t>
+        </is>
+      </c>
+      <c r="H70" s="55" t="inlineStr">
+        <is>
+          <t>Conclusões, limitações do estudo e recomendações</t>
+        </is>
+      </c>
+      <c r="I70" s="52" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="J70" s="52" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="48" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" s="49" t="inlineStr">
+        <is>
+          <t>17/04/2027</t>
+        </is>
+      </c>
+      <c r="C71" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D71" s="49" t="inlineStr">
+        <is>
+          <t>08h00–10h00</t>
+        </is>
+      </c>
+      <c r="E71" s="49" t="inlineStr">
+        <is>
+          <t>1.º tempo</t>
+        </is>
+      </c>
+      <c r="F71" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G71" s="51" t="inlineStr">
+        <is>
+          <t>UV — Ética, deontologia e direitos</t>
+        </is>
+      </c>
+      <c r="H71" s="51" t="inlineStr">
+        <is>
+          <t>Sigilo profissional, consentimento informado e direitos do doente</t>
+        </is>
+      </c>
+      <c r="I71" s="48" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="J71" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>17/04/2027</t>
+        </is>
+      </c>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t>10h00–10h30</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>Intervalo</t>
+        </is>
+      </c>
+      <c r="F72" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="10" t="inlineStr">
+        <is>
+          <t>Intervalo regulamentar</t>
+        </is>
+      </c>
+      <c r="I72" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J72" s="7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="48" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" s="49" t="inlineStr">
+        <is>
+          <t>17/04/2027</t>
+        </is>
+      </c>
+      <c r="C73" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D73" s="49" t="inlineStr">
+        <is>
+          <t>10h30–12h30</t>
+        </is>
+      </c>
+      <c r="E73" s="49" t="inlineStr">
+        <is>
+          <t>2.º tempo</t>
+        </is>
+      </c>
+      <c r="F73" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G73" s="51" t="inlineStr">
+        <is>
+          <t>UV — Ética, deontologia e direitos</t>
+        </is>
+      </c>
+      <c r="H73" s="51" t="inlineStr">
+        <is>
+          <t>Sigilo profissional, consentimento informado e direitos do doente</t>
+        </is>
+      </c>
+      <c r="I73" s="48" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="J73" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="52" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" s="53" t="inlineStr">
+        <is>
+          <t>17/04/2027</t>
+        </is>
+      </c>
+      <c r="C74" s="53" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D74" s="53" t="inlineStr">
+        <is>
+          <t>12h30–16h00</t>
+        </is>
+      </c>
+      <c r="E74" s="53" t="inlineStr">
+        <is>
+          <t>Bloco de projecto</t>
+        </is>
+      </c>
+      <c r="F74" s="54" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="G74" s="55" t="inlineStr">
+        <is>
+          <t>UV — Discussão, conclusões e redacção</t>
+        </is>
+      </c>
+      <c r="H74" s="55" t="inlineStr">
+        <is>
+          <t>Redacção do trabalho: estrutura formal, capa, índice e paginação</t>
+        </is>
+      </c>
+      <c r="I74" s="52" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J74" s="52" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="48" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" s="49" t="inlineStr">
+        <is>
+          <t>24/04/2027</t>
+        </is>
+      </c>
+      <c r="C75" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D75" s="49" t="inlineStr">
+        <is>
+          <t>08h00–10h00</t>
+        </is>
+      </c>
+      <c r="E75" s="49" t="inlineStr">
+        <is>
+          <t>1.º tempo</t>
+        </is>
+      </c>
+      <c r="F75" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G75" s="51" t="inlineStr">
+        <is>
+          <t>UVI — Gestão da informação</t>
+        </is>
+      </c>
+      <c r="H75" s="51" t="inlineStr">
+        <is>
+          <t>Gestão da informação: registos, estatística do serviço e relatório mensal</t>
+        </is>
+      </c>
+      <c r="I75" s="48" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J75" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>24/04/2027</t>
+        </is>
+      </c>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>10h00–10h30</t>
+        </is>
+      </c>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>Intervalo</t>
+        </is>
+      </c>
+      <c r="F76" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H76" s="10" t="inlineStr">
+        <is>
+          <t>Intervalo regulamentar</t>
+        </is>
+      </c>
+      <c r="I76" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J76" s="7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="48" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" s="49" t="inlineStr">
+        <is>
+          <t>24/04/2027</t>
+        </is>
+      </c>
+      <c r="C77" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D77" s="49" t="inlineStr">
+        <is>
+          <t>10h30–12h30</t>
+        </is>
+      </c>
+      <c r="E77" s="49" t="inlineStr">
+        <is>
+          <t>2.º tempo</t>
+        </is>
+      </c>
+      <c r="F77" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G77" s="51" t="inlineStr">
+        <is>
+          <t>UVI — Gestão da informação</t>
+        </is>
+      </c>
+      <c r="H77" s="51" t="inlineStr">
+        <is>
+          <t>Gestão da informação: registos, estatística do serviço e relatório mensal</t>
+        </is>
+      </c>
+      <c r="I77" s="48" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J77" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="52" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" s="53" t="inlineStr">
+        <is>
+          <t>24/04/2027</t>
+        </is>
+      </c>
+      <c r="C78" s="53" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D78" s="53" t="inlineStr">
+        <is>
+          <t>12h30–16h00</t>
+        </is>
+      </c>
+      <c r="E78" s="53" t="inlineStr">
+        <is>
+          <t>Bloco de projecto</t>
+        </is>
+      </c>
+      <c r="F78" s="54" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="G78" s="55" t="inlineStr">
+        <is>
+          <t>UV — Discussão, conclusões e redacção</t>
+        </is>
+      </c>
+      <c r="H78" s="55" t="inlineStr">
+        <is>
+          <t>4.ª pré-defesa — apresentação do trabalho completo perante júri</t>
+        </is>
+      </c>
+      <c r="I78" s="52" t="inlineStr">
+        <is>
+          <t>Avaliação prática</t>
+        </is>
+      </c>
+      <c r="J78" s="52" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="48" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" s="49" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C79" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D79" s="49" t="inlineStr">
+        <is>
+          <t>08h00–10h00</t>
+        </is>
+      </c>
+      <c r="E79" s="49" t="inlineStr">
+        <is>
+          <t>1.º tempo</t>
+        </is>
+      </c>
+      <c r="F79" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G79" s="51" t="inlineStr">
+        <is>
+          <t>UVII — Relações de trabalho</t>
+        </is>
+      </c>
+      <c r="H79" s="51" t="inlineStr">
+        <is>
+          <t>Actividade do Dia do Trabalhador — o trabalho de enfermagem em Angola: mesa-redonda com professores e formandos</t>
+        </is>
+      </c>
+      <c r="I79" s="48" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="J79" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C80" s="8" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>10h00–10h30</t>
+        </is>
+      </c>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>Intervalo</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="10" t="inlineStr">
+        <is>
+          <t>Intervalo regulamentar</t>
+        </is>
+      </c>
+      <c r="I80" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J80" s="7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="48" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" s="49" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C81" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D81" s="49" t="inlineStr">
+        <is>
+          <t>10h30–12h30</t>
+        </is>
+      </c>
+      <c r="E81" s="49" t="inlineStr">
+        <is>
+          <t>2.º tempo</t>
+        </is>
+      </c>
+      <c r="F81" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G81" s="51" t="inlineStr">
+        <is>
+          <t>UVII — Relações de trabalho</t>
+        </is>
+      </c>
+      <c r="H81" s="51" t="inlineStr">
+        <is>
+          <t>Actividade do Dia do Trabalhador — o trabalho de enfermagem em Angola: mesa-redonda com professores e formandos</t>
+        </is>
+      </c>
+      <c r="I81" s="48" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="J81" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="52" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" s="53" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C82" s="53" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D82" s="53" t="inlineStr">
+        <is>
+          <t>12h30–16h00</t>
+        </is>
+      </c>
+      <c r="E82" s="53" t="inlineStr">
+        <is>
+          <t>Bloco de projecto</t>
+        </is>
+      </c>
+      <c r="F82" s="54" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="G82" s="55" t="inlineStr">
+        <is>
+          <t>UVI — Preparação da defesa</t>
+        </is>
+      </c>
+      <c r="H82" s="55" t="inlineStr">
+        <is>
+          <t>Actividade do Dia do Trabalhador — exposição dos projectos à comunidade escolar</t>
+        </is>
+      </c>
+      <c r="I82" s="52" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J82" s="52" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="48" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" s="49" t="inlineStr">
+        <is>
+          <t>08/05/2027</t>
+        </is>
+      </c>
+      <c r="C83" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D83" s="49" t="inlineStr">
+        <is>
+          <t>08h00–10h00</t>
+        </is>
+      </c>
+      <c r="E83" s="49" t="inlineStr">
+        <is>
+          <t>1.º tempo</t>
+        </is>
+      </c>
+      <c r="F83" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G83" s="51" t="inlineStr">
+        <is>
+          <t>UVII — Relações de trabalho</t>
+        </is>
+      </c>
+      <c r="H83" s="51" t="inlineStr">
+        <is>
+          <t>Gestão de conflitos e comunicação institucional</t>
+        </is>
+      </c>
+      <c r="I83" s="48" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="J83" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>08/05/2027</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>10h00–10h30</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>Intervalo</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G84" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H84" s="10" t="inlineStr">
+        <is>
+          <t>Intervalo regulamentar</t>
+        </is>
+      </c>
+      <c r="I84" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J84" s="7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="48" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" s="49" t="inlineStr">
+        <is>
+          <t>08/05/2027</t>
+        </is>
+      </c>
+      <c r="C85" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D85" s="49" t="inlineStr">
+        <is>
+          <t>10h30–12h30</t>
+        </is>
+      </c>
+      <c r="E85" s="49" t="inlineStr">
+        <is>
+          <t>2.º tempo</t>
+        </is>
+      </c>
+      <c r="F85" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G85" s="51" t="inlineStr">
+        <is>
+          <t>UVII — Relações de trabalho</t>
+        </is>
+      </c>
+      <c r="H85" s="51" t="inlineStr">
+        <is>
+          <t>Gestão de conflitos e comunicação institucional</t>
+        </is>
+      </c>
+      <c r="I85" s="48" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="J85" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="52" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" s="53" t="inlineStr">
+        <is>
+          <t>08/05/2027</t>
+        </is>
+      </c>
+      <c r="C86" s="53" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D86" s="53" t="inlineStr">
+        <is>
+          <t>12h30–16h00</t>
+        </is>
+      </c>
+      <c r="E86" s="53" t="inlineStr">
+        <is>
+          <t>Bloco de projecto</t>
+        </is>
+      </c>
+      <c r="F86" s="54" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="G86" s="55" t="inlineStr">
+        <is>
+          <t>UVI — Preparação da defesa</t>
+        </is>
+      </c>
+      <c r="H86" s="55" t="inlineStr">
+        <is>
+          <t>Normas de citação e referências bibliográficas; revisão do texto após a entrega</t>
+        </is>
+      </c>
+      <c r="I86" s="52" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J86" s="52" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="48" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" s="49" t="inlineStr">
+        <is>
+          <t>15/05/2027</t>
+        </is>
+      </c>
+      <c r="C87" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D87" s="49" t="inlineStr">
+        <is>
+          <t>08h00–10h00</t>
+        </is>
+      </c>
+      <c r="E87" s="49" t="inlineStr">
+        <is>
+          <t>1.º tempo</t>
+        </is>
+      </c>
+      <c r="F87" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G87" s="51" t="inlineStr">
+        <is>
+          <t>UVII — Relações de trabalho</t>
+        </is>
+      </c>
+      <c r="H87" s="51" t="inlineStr">
+        <is>
+          <t>Trabalho em equipa multiprofissional e condução de reuniões de serviço</t>
+        </is>
+      </c>
+      <c r="I87" s="48" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="J87" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>15/05/2027</t>
+        </is>
+      </c>
+      <c r="C88" s="8" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t>10h00–10h30</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>Intervalo</t>
+        </is>
+      </c>
+      <c r="F88" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G88" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H88" s="10" t="inlineStr">
+        <is>
+          <t>Intervalo regulamentar</t>
+        </is>
+      </c>
+      <c r="I88" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J88" s="7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="48" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" s="49" t="inlineStr">
+        <is>
+          <t>15/05/2027</t>
+        </is>
+      </c>
+      <c r="C89" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D89" s="49" t="inlineStr">
+        <is>
+          <t>10h30–12h30</t>
+        </is>
+      </c>
+      <c r="E89" s="49" t="inlineStr">
+        <is>
+          <t>2.º tempo</t>
+        </is>
+      </c>
+      <c r="F89" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G89" s="51" t="inlineStr">
+        <is>
+          <t>UVII — Relações de trabalho</t>
+        </is>
+      </c>
+      <c r="H89" s="51" t="inlineStr">
+        <is>
+          <t>Trabalho em equipa multiprofissional e condução de reuniões de serviço</t>
+        </is>
+      </c>
+      <c r="I89" s="48" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="J89" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="52" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" s="53" t="inlineStr">
+        <is>
+          <t>15/05/2027</t>
+        </is>
+      </c>
+      <c r="C90" s="53" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D90" s="53" t="inlineStr">
+        <is>
+          <t>12h30–16h00</t>
+        </is>
+      </c>
+      <c r="E90" s="53" t="inlineStr">
+        <is>
+          <t>Bloco de projecto</t>
+        </is>
+      </c>
+      <c r="F90" s="54" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="G90" s="55" t="inlineStr">
+        <is>
+          <t>UVI — Preparação da defesa</t>
+        </is>
+      </c>
+      <c r="H90" s="55" t="inlineStr">
+        <is>
+          <t>Preparação da apresentação oral: estrutura, meios de apoio e distribuição de papéis no grupo</t>
+        </is>
+      </c>
+      <c r="I90" s="52" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J90" s="52" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="48" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" s="49" t="inlineStr">
+        <is>
+          <t>22/05/2027</t>
+        </is>
+      </c>
+      <c r="C91" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D91" s="49" t="inlineStr">
+        <is>
+          <t>08h00–10h00</t>
+        </is>
+      </c>
+      <c r="E91" s="49" t="inlineStr">
+        <is>
+          <t>1.º tempo</t>
+        </is>
+      </c>
+      <c r="F91" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G91" s="51" t="inlineStr">
+        <is>
+          <t>UVIII — Empreendedorismo e inserção profissional</t>
+        </is>
+      </c>
+      <c r="H91" s="51" t="inlineStr">
+        <is>
+          <t>Empreendedorismo em saúde e projectos de intervenção comunitária</t>
+        </is>
+      </c>
+      <c r="I91" s="48" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="J91" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>22/05/2027</t>
+        </is>
+      </c>
+      <c r="C92" s="8" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D92" s="8" t="inlineStr">
+        <is>
+          <t>10h00–10h30</t>
+        </is>
+      </c>
+      <c r="E92" s="8" t="inlineStr">
+        <is>
+          <t>Intervalo</t>
+        </is>
+      </c>
+      <c r="F92" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G92" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H92" s="10" t="inlineStr">
+        <is>
+          <t>Intervalo regulamentar</t>
+        </is>
+      </c>
+      <c r="I92" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J92" s="7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="48" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" s="49" t="inlineStr">
+        <is>
+          <t>22/05/2027</t>
+        </is>
+      </c>
+      <c r="C93" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D93" s="49" t="inlineStr">
+        <is>
+          <t>10h30–12h30</t>
+        </is>
+      </c>
+      <c r="E93" s="49" t="inlineStr">
+        <is>
+          <t>2.º tempo</t>
+        </is>
+      </c>
+      <c r="F93" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G93" s="51" t="inlineStr">
+        <is>
+          <t>UVIII — Empreendedorismo e inserção profissional</t>
+        </is>
+      </c>
+      <c r="H93" s="51" t="inlineStr">
+        <is>
+          <t>Empreendedorismo em saúde e projectos de intervenção comunitária</t>
+        </is>
+      </c>
+      <c r="I93" s="48" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="J93" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="52" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" s="53" t="inlineStr">
+        <is>
+          <t>22/05/2027</t>
+        </is>
+      </c>
+      <c r="C94" s="53" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D94" s="53" t="inlineStr">
+        <is>
+          <t>12h30–16h00</t>
+        </is>
+      </c>
+      <c r="E94" s="53" t="inlineStr">
+        <is>
+          <t>Bloco de projecto</t>
+        </is>
+      </c>
+      <c r="F94" s="54" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="G94" s="55" t="inlineStr">
+        <is>
+          <t>UVI — Preparação da defesa</t>
+        </is>
+      </c>
+      <c r="H94" s="55" t="inlineStr">
+        <is>
+          <t>Técnicas de apresentação oral e resposta às perguntas do júri</t>
+        </is>
+      </c>
+      <c r="I94" s="52" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J94" s="52" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="48" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" s="49" t="inlineStr">
+        <is>
+          <t>29/05/2027</t>
+        </is>
+      </c>
+      <c r="C95" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D95" s="49" t="inlineStr">
+        <is>
+          <t>08h00–10h00</t>
+        </is>
+      </c>
+      <c r="E95" s="49" t="inlineStr">
+        <is>
+          <t>1.º tempo</t>
+        </is>
+      </c>
+      <c r="F95" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G95" s="51" t="inlineStr">
+        <is>
+          <t>UVIII — Empreendedorismo e inserção profissional</t>
+        </is>
+      </c>
+      <c r="H95" s="51" t="inlineStr">
+        <is>
+          <t>Inserção profissional: currículo, entrevista e primeiro emprego; avaliação final da disciplina</t>
+        </is>
+      </c>
+      <c r="I95" s="48" t="inlineStr">
+        <is>
+          <t>Avaliação prática</t>
+        </is>
+      </c>
+      <c r="J95" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>29/05/2027</t>
+        </is>
+      </c>
+      <c r="C96" s="8" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D96" s="8" t="inlineStr">
+        <is>
+          <t>10h00–10h30</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>Intervalo</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G96" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H96" s="10" t="inlineStr">
+        <is>
+          <t>Intervalo regulamentar</t>
+        </is>
+      </c>
+      <c r="I96" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J96" s="7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="48" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" s="49" t="inlineStr">
+        <is>
+          <t>29/05/2027</t>
+        </is>
+      </c>
+      <c r="C97" s="49" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D97" s="49" t="inlineStr">
+        <is>
+          <t>10h30–12h30</t>
+        </is>
+      </c>
+      <c r="E97" s="49" t="inlineStr">
+        <is>
+          <t>2.º tempo</t>
+        </is>
+      </c>
+      <c r="F97" s="50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="G97" s="51" t="inlineStr">
+        <is>
+          <t>UVIII — Empreendedorismo e inserção profissional</t>
+        </is>
+      </c>
+      <c r="H97" s="51" t="inlineStr">
+        <is>
+          <t>Inserção profissional: currículo, entrevista e primeiro emprego; avaliação final da disciplina</t>
+        </is>
+      </c>
+      <c r="I97" s="48" t="inlineStr">
+        <is>
+          <t>Avaliação prática</t>
+        </is>
+      </c>
+      <c r="J97" s="48" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="52" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" s="53" t="inlineStr">
+        <is>
+          <t>29/05/2027</t>
+        </is>
+      </c>
+      <c r="C98" s="53" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D98" s="53" t="inlineStr">
+        <is>
+          <t>12h30–16h00</t>
+        </is>
+      </c>
+      <c r="E98" s="53" t="inlineStr">
+        <is>
+          <t>Bloco de projecto</t>
+        </is>
+      </c>
+      <c r="F98" s="54" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="G98" s="55" t="inlineStr">
+        <is>
+          <t>UVI — Preparação da defesa</t>
+        </is>
+      </c>
+      <c r="H98" s="55" t="inlineStr">
+        <is>
+          <t>Ensaio geral da defesa perante júri simulado</t>
+        </is>
+      </c>
+      <c r="I98" s="52" t="inlineStr">
+        <is>
+          <t>Avaliação prática</t>
+        </is>
+      </c>
+      <c r="J98" s="52" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="F100" s="47" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="H100" s="56">
+        <f>SUMIF(Sábados!$F$3:$F$98,"GEN",Sábados!$J$3:$J$98)/60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="F101" s="47" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="H101" s="56">
+        <f>SUMIF(Sábados!$F$3:$F$98,"PT",Sábados!$J$3:$J$98)/60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="F102" s="47" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="H102" s="57">
+        <f>H100+H101</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:J98"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Estágios, pré-defesas e defesa de fim de curso</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="58" t="inlineStr">
+        <is>
+          <t>Campo</t>
+        </is>
+      </c>
+      <c r="B3" s="58" t="inlineStr">
+        <is>
+          <t>Estágio preliminar</t>
+        </is>
+      </c>
+      <c r="C3" s="58" t="inlineStr">
+        <is>
+          <t>Estágio curricular</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="58" t="inlineStr">
+        <is>
+          <t>Encargo</t>
+        </is>
+      </c>
+      <c r="B4" s="58" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="C4" s="58" t="inlineStr">
+        <is>
+          <t>Regime</t>
+        </is>
+      </c>
+      <c r="D4" s="58" t="inlineStr">
+        <is>
+          <t>Prazo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="59" t="inlineStr">
+        <is>
+          <t>Confirmação do III.º Módulo</t>
+        </is>
+      </c>
+      <c r="B5" s="60" t="inlineStr">
+        <is>
+          <t>Hospital do Capalanga (Viana)</t>
+        </is>
+      </c>
+      <c r="C5" s="60" t="inlineStr">
+        <is>
+          <t>Acto único</t>
+        </is>
+      </c>
+      <c r="D5" s="60" t="inlineStr">
+        <is>
+          <t>No início do módulo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="59" t="inlineStr">
+        <is>
+          <t>Mensalidade</t>
+        </is>
+      </c>
+      <c r="B6" s="60" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="C6" s="60" t="inlineStr">
+        <is>
+          <t>9 mensalidades, de Outubro de 2026 a Junho de 2027</t>
+        </is>
+      </c>
+      <c r="D6" s="60" t="inlineStr">
+        <is>
+          <t>Até ao dia 10 de cada mês</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="59" t="inlineStr">
+        <is>
+          <t>Comparticipação para aulas práticas</t>
+        </is>
+      </c>
+      <c r="B7" s="60" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="60" t="inlineStr">
+        <is>
+          <t>Acto único</t>
+        </is>
+      </c>
+      <c r="D7" s="60" t="inlineStr">
+        <is>
+          <t>No início do módulo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="59" t="inlineStr">
+        <is>
+          <t>Túnica</t>
+        </is>
+      </c>
+      <c r="B8" s="60" t="inlineStr">
+        <is>
+          <t>05/01/2027</t>
+        </is>
+      </c>
+      <c r="C8" s="60" t="inlineStr">
+        <is>
+          <t>Acto único</t>
+        </is>
+      </c>
+      <c r="D8" s="60" t="inlineStr">
+        <is>
+          <t>No início do módulo</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="59" t="inlineStr">
+        <is>
+          <t>Estágio preliminar (3 meses)</t>
+        </is>
+      </c>
+      <c r="B9" s="60" t="inlineStr">
+        <is>
+          <t>3 meses</t>
+        </is>
+      </c>
+      <c r="C9" s="60" t="inlineStr">
+        <is>
+          <t>Acto único</t>
+        </is>
+      </c>
+      <c r="D9" s="60" t="inlineStr">
+        <is>
+          <t>Antes do início do estágio</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="59" t="inlineStr">
+        <is>
+          <t>Estágio curricular (6 meses)</t>
+        </is>
+      </c>
+      <c r="B10" s="60" t="inlineStr">
+        <is>
+          <t>Segunda, quarta e sexta-feira e domingo, conforme a escala do hospital</t>
+        </is>
+      </c>
+      <c r="C10" s="60" t="inlineStr">
+        <is>
+          <t>Acto único</t>
+        </is>
+      </c>
+      <c r="D10" s="60" t="inlineStr">
+        <is>
+          <t>Até à primeira semana de Janeiro de 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="59" t="inlineStr">
+        <is>
+          <t>Tutoria do Projecto Tecnológico</t>
+        </is>
+      </c>
+      <c r="B11" s="60" t="inlineStr">
+        <is>
+          <t>10 horas por dia</t>
+        </is>
+      </c>
+      <c r="C11" s="60" t="inlineStr">
+        <is>
+          <t>Pagamento único ao tutor</t>
+        </is>
+      </c>
+      <c r="D11" s="60" t="inlineStr">
+        <is>
+          <t>Durante o módulo</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="59" t="inlineStr">
+        <is>
+          <t>Manuais de apoio</t>
+        </is>
+      </c>
+      <c r="B12" s="60" t="inlineStr">
+        <is>
+          <t>A fixar pela escala do hospital [a confirmar]</t>
+        </is>
+      </c>
+      <c r="C12" s="60" t="inlineStr">
+        <is>
+          <t>Conjunto completo</t>
+        </is>
+      </c>
+      <c r="D12" s="60" t="inlineStr">
+        <is>
+          <t>Durante o módulo</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="59" t="inlineStr">
+        <is>
+          <t>Declaração para obtenção da licença de aprendizagem</t>
+        </is>
+      </c>
+      <c r="B13" s="60" t="inlineStr">
+        <is>
+          <t>Edilson de Almeida (supervisão pela escola)</t>
+        </is>
+      </c>
+      <c r="C13" s="60" t="inlineStr">
+        <is>
+          <t>Acto único</t>
+        </is>
+      </c>
+      <c r="D13" s="60" t="inlineStr">
+        <is>
+          <t>Até 10 de Outubro de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="59" t="inlineStr">
+        <is>
+          <t>Termo de frequência</t>
+        </is>
+      </c>
+      <c r="B14" s="60" t="inlineStr">
+        <is>
+          <t>Tutor do serviço a designar pelo hospital [a confirmar]</t>
+        </is>
+      </c>
+      <c r="C14" s="60" t="inlineStr">
+        <is>
+          <t>Acto único</t>
+        </is>
+      </c>
+      <c r="D14" s="60" t="inlineStr">
+        <is>
+          <t>Até 30 de Novembro de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="59" t="inlineStr">
+        <is>
+          <t>Declaração de frequência</t>
+        </is>
+      </c>
+      <c r="B15" s="60" t="inlineStr">
+        <is>
+          <t>60 % da classificação da componente de estágio</t>
+        </is>
+      </c>
+      <c r="C15" s="60" t="inlineStr">
+        <is>
+          <t>Acto único</t>
+        </is>
+      </c>
+      <c r="D15" s="60" t="inlineStr">
+        <is>
+          <t>No fim do curso</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="59" t="inlineStr">
+        <is>
+          <t>Mesa de júri da defesa</t>
+        </is>
+      </c>
+      <c r="B16" s="60" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C16" s="60" t="inlineStr">
+        <is>
+          <t>Acto único</t>
+        </is>
+      </c>
+      <c r="D16" s="60" t="inlineStr">
+        <is>
+          <t>Antes da defesa</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="59" t="inlineStr">
+        <is>
+          <t>Sala da defesa</t>
+        </is>
+      </c>
+      <c r="C17" s="60" t="inlineStr">
+        <is>
+          <t>Acto único</t>
+        </is>
+      </c>
+      <c r="D17" s="60" t="inlineStr">
+        <is>
+          <t>Antes da defesa</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="58" t="inlineStr">
+        <is>
+          <t>Faça</t>
+        </is>
+      </c>
+      <c r="B18" s="61" t="inlineStr">
+        <is>
+          <t>Folha de presenças assinada pelo serviço; Relatório de estágio elaborado pelo formando; Ficha de avaliação preenchida pelo hospital</t>
+        </is>
+      </c>
+      <c r="C18" s="60" t="inlineStr">
+        <is>
+          <t>Acto único</t>
+        </is>
+      </c>
+      <c r="D18" s="60" t="inlineStr">
+        <is>
+          <t>Antes da defesa</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="58" t="inlineStr">
+        <is>
+          <t>Total do módulo por formando</t>
+        </is>
+      </c>
+      <c r="C19" s="61" t="inlineStr">
+        <is>
+          <t>a mensalidade conta 9 vezes</t>
+        </is>
+      </c>
+      <c r="D19" s="61" t="inlineStr">
+        <is>
+          <t>conferência: 375.600 Kz</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="58" t="inlineStr">
+        <is>
+          <t>Momento</t>
+        </is>
+      </c>
+      <c r="B20" s="58" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="C20" s="58" t="inlineStr">
+        <is>
+          <t>Observações</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="59" t="inlineStr">
+        <is>
+          <t>1.ª pré-defesa</t>
+        </is>
+      </c>
+      <c r="B21" s="60" t="inlineStr">
+        <is>
+          <t>30/01/2027</t>
+        </is>
+      </c>
+      <c r="C21" s="60" t="inlineStr">
+        <is>
+          <t>Sábado, no bloco de projecto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="58" t="inlineStr">
+        <is>
+          <t>Encargo</t>
+        </is>
+      </c>
+      <c r="B22" s="58" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="C22" s="58" t="inlineStr">
+        <is>
+          <t>Regime</t>
+        </is>
+      </c>
+      <c r="D22" s="58" t="inlineStr">
+        <is>
+          <t>Quando se aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="59" t="inlineStr">
+        <is>
+          <t>Multa por atraso no pagamento da mensalidade</t>
+        </is>
+      </c>
+      <c r="B23" s="60" t="inlineStr">
+        <is>
+          <t>27/03/2027</t>
+        </is>
+      </c>
+      <c r="C23" s="60" t="inlineStr">
+        <is>
+          <t>Por mensalidade em atraso</t>
+        </is>
+      </c>
+      <c r="D23" s="60" t="inlineStr">
+        <is>
+          <t>A partir do dia 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="59" t="inlineStr">
+        <is>
+          <t>Recurso por disciplina</t>
+        </is>
+      </c>
+      <c r="B24" s="60" t="inlineStr">
+        <is>
+          <t>24/04/2027</t>
+        </is>
+      </c>
+      <c r="C24" s="60" t="inlineStr">
+        <is>
+          <t>Por disciplina</t>
+        </is>
+      </c>
+      <c r="D24" s="60" t="inlineStr">
+        <is>
+          <t>Entre uma semana após as provas e 15 dias após a publicação das pautas</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="59" t="inlineStr">
+        <is>
+          <t>Recurso da defesa</t>
+        </is>
+      </c>
+      <c r="B25" s="60" t="inlineStr">
+        <is>
+          <t>29/05/2027</t>
+        </is>
+      </c>
+      <c r="C25" s="60" t="inlineStr">
+        <is>
+          <t>Acto único</t>
+        </is>
+      </c>
+      <c r="D25" s="60" t="inlineStr">
+        <is>
+          <t>Quinze dias após a defesa (18/06/2027)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="59" t="inlineStr">
+        <is>
+          <t>Entrega do trabalho</t>
+        </is>
+      </c>
+      <c r="B26" s="60" t="inlineStr">
+        <is>
+          <t>03/05/2027</t>
+        </is>
+      </c>
+      <c r="C26" s="60" t="inlineStr">
+        <is>
+          <t>Um mês antes da defesa</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="59" t="inlineStr">
+        <is>
+          <t>Defesa de fim de curso</t>
+        </is>
+      </c>
+      <c r="B27" s="60" t="inlineStr">
+        <is>
+          <t>03/06/2027</t>
+        </is>
+      </c>
+      <c r="C27" s="60" t="inlineStr">
+        <is>
+          <t>Júri presidido pela escola-mãe, composto por um presidente e três vogais</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="58" t="inlineStr">
+        <is>
+          <t>Encargo</t>
+        </is>
+      </c>
+      <c r="B28" s="58" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="C28" s="58" t="inlineStr">
+        <is>
+          <t>Observações</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="59" t="inlineStr">
+        <is>
+          <t>Confirmação ou renovação de matrícula para o módulo seguinte</t>
+        </is>
+      </c>
+      <c r="C29" s="60" t="inlineStr">
+        <is>
+          <t>No início do módulo seguinte</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="59" t="inlineStr">
+        <is>
+          <t>Certificado de conclusão do módulo</t>
+        </is>
+      </c>
+      <c r="B30" s="60" t="inlineStr">
+        <is>
+          <t>a definir</t>
+        </is>
+      </c>
+      <c r="C30" s="60" t="inlineStr">
+        <is>
+          <t>Valor por definir [a confirmar]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="59" t="inlineStr">
+        <is>
+          <t>Segunda via de documento</t>
+        </is>
+      </c>
+      <c r="B31" s="60" t="inlineStr">
+        <is>
+          <t>a definir</t>
+        </is>
+      </c>
+      <c r="C31" s="60" t="inlineStr">
+        <is>
+          <t>Valor por definir [a confirmar]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="60" t="inlineStr">
+        <is>
+          <t>O pagamento é efectuado exclusivamente por terminal de pagamento automático (TPA).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="60" t="inlineStr">
+        <is>
+          <t>Não há descontos por pagamento adiantado, por irmãos nem por antiguidade.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="60" t="inlineStr">
+        <is>
+          <t>A mensalidade vence-se até ao dia 10 de cada mês; a partir do dia 11 acresce a multa de 2.000 Kz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="60" t="inlineStr">
+        <is>
+          <t>O formando com mensalidades em atraso não é admitido à defesa de fim de curso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="60" t="inlineStr">
+        <is>
+          <t>Os documentos e as declarações só são emitidos a formandos com a situação de propinas regularizada.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Condições financeiras — turma MIDAS — NOV-A, III.º Módulo, 2026/2027 (valores em kwanzas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="62" t="inlineStr">
+        <is>
+          <t>Encargos do módulo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="63" t="n">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="63" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="63" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="63" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="63" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="63" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="63" t="n">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="63" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="63" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="63" t="n">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="63" t="n">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="63" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="63" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="63" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="64">
+        <f>SUM(B5:B18)+B6*8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="62" t="inlineStr">
+        <is>
+          <t>Encargos eventuais</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="63" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="63" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="63" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="62" t="inlineStr">
+        <is>
+          <t>Encargos posteriores e valores por definir</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="63" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="62" t="inlineStr">
+        <is>
+          <t>Regras de pagamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A36:D36"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/formacao/enfermagem-geral-nov-a/Cronograma-Enfermagem-Geral-III-Modulo-NOV-A.xlsx
+++ b/docs/formacao/enfermagem-geral-nov-a/Cronograma-Enfermagem-Geral-III-Modulo-NOV-A.xlsx
@@ -20684,7 +20684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -21020,7 +21020,7 @@
     <row r="18">
       <c r="A18" s="58" t="inlineStr">
         <is>
-          <t>Faça</t>
+          <t>Faixa de finalista</t>
         </is>
       </c>
       <c r="B18" s="61" t="inlineStr">
@@ -21232,19 +21232,24 @@
     <row r="29">
       <c r="A29" s="59" t="inlineStr">
         <is>
-          <t>Confirmação ou renovação de matrícula para o módulo seguinte</t>
+          <t>Certificado de conclusão do módulo</t>
+        </is>
+      </c>
+      <c r="B29" s="60" t="inlineStr">
+        <is>
+          <t>a definir</t>
         </is>
       </c>
       <c r="C29" s="60" t="inlineStr">
         <is>
-          <t>No início do módulo seguinte</t>
+          <t>Valor por definir [a confirmar]</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="59" t="inlineStr">
         <is>
-          <t>Certificado de conclusão do módulo</t>
+          <t>Segunda via de documento</t>
         </is>
       </c>
       <c r="B30" s="60" t="inlineStr">
@@ -21258,53 +21263,43 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="59" t="inlineStr">
-        <is>
-          <t>Segunda via de documento</t>
-        </is>
-      </c>
-      <c r="B31" s="60" t="inlineStr">
-        <is>
-          <t>a definir</t>
-        </is>
-      </c>
-      <c r="C31" s="60" t="inlineStr">
-        <is>
-          <t>Valor por definir [a confirmar]</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="60" t="inlineStr">
-        <is>
-          <t>O pagamento é efectuado exclusivamente por terminal de pagamento automático (TPA).</t>
+    <row r="32">
+      <c r="A32" s="60" t="inlineStr">
+        <is>
+          <t>A confirmação de matrícula do II.º Módulo custa 10.000 Kz. A confirmação do III.º Módulo, aplicável a esta turma, custa 1.600 Kz e é o valor inscrito no quadro dos encargos do módulo.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="60" t="inlineStr">
         <is>
-          <t>Não há descontos por pagamento adiantado, por irmãos nem por antiguidade.</t>
+          <t>O pagamento é efectuado exclusivamente por terminal de pagamento automático (TPA).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="60" t="inlineStr">
         <is>
-          <t>A mensalidade vence-se até ao dia 10 de cada mês; a partir do dia 11 acresce a multa de 2.000 Kz.</t>
+          <t>Não há descontos por pagamento adiantado, por irmãos nem por antiguidade.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="60" t="inlineStr">
         <is>
-          <t>O formando com mensalidades em atraso não é admitido à defesa de fim de curso.</t>
+          <t>A mensalidade vence-se até ao dia 10 de cada mês; a partir do dia 11 acresce a multa de 2.000 Kz.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="60" t="inlineStr">
+        <is>
+          <t>O formando com mensalidades em atraso não é admitido à defesa de fim de curso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="60" t="inlineStr">
         <is>
           <t>Os documentos e as declarações só são emitidos a formandos com a situação de propinas regularizada.</t>
         </is>
@@ -21324,7 +21319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -21448,29 +21443,25 @@
     <row r="27">
       <c r="A27" s="62" t="inlineStr">
         <is>
-          <t>Encargos posteriores e valores por definir</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="63" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="62" t="inlineStr">
+          <t>Valores por definir</t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="34">
+      <c r="A34" s="62" t="inlineStr">
         <is>
           <t>Regras de pagamento</t>
         </is>
       </c>
     </row>
-    <row r="34"/>
     <row r="35"/>
     <row r="36"/>
     <row r="37"/>
     <row r="38"/>
+    <row r="39"/>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A37:D37"/>
     <mergeCell ref="A27:D27"/>
@@ -21479,7 +21470,8 @@
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A32:D32"/>
     <mergeCell ref="A36:D36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/formacao/enfermagem-geral-nov-a/Cronograma-Enfermagem-Geral-III-Modulo-NOV-A.xlsx
+++ b/docs/formacao/enfermagem-geral-nov-a/Cronograma-Enfermagem-Geral-III-Modulo-NOV-A.xlsx
@@ -20684,7 +20684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -20751,7 +20751,7 @@
       </c>
       <c r="C5" s="60" t="inlineStr">
         <is>
-          <t>Acto único</t>
+          <t>Acto único, por formando</t>
         </is>
       </c>
       <c r="D5" s="60" t="inlineStr">
@@ -20795,7 +20795,7 @@
       </c>
       <c r="C7" s="60" t="inlineStr">
         <is>
-          <t>Acto único</t>
+          <t>Acto único, por formando</t>
         </is>
       </c>
       <c r="D7" s="60" t="inlineStr">
@@ -20817,7 +20817,7 @@
       </c>
       <c r="C8" s="60" t="inlineStr">
         <is>
-          <t>Acto único</t>
+          <t>Acto único, por formando</t>
         </is>
       </c>
       <c r="D8" s="60" t="inlineStr">
@@ -20839,7 +20839,7 @@
       </c>
       <c r="C9" s="60" t="inlineStr">
         <is>
-          <t>Acto único</t>
+          <t>Acto único, por formando</t>
         </is>
       </c>
       <c r="D9" s="60" t="inlineStr">
@@ -20861,7 +20861,7 @@
       </c>
       <c r="C10" s="60" t="inlineStr">
         <is>
-          <t>Acto único</t>
+          <t>Acto único, por formando</t>
         </is>
       </c>
       <c r="D10" s="60" t="inlineStr">
@@ -20927,7 +20927,7 @@
       </c>
       <c r="C13" s="60" t="inlineStr">
         <is>
-          <t>Acto único</t>
+          <t>Acto único, por formando</t>
         </is>
       </c>
       <c r="D13" s="60" t="inlineStr">
@@ -20949,7 +20949,7 @@
       </c>
       <c r="C14" s="60" t="inlineStr">
         <is>
-          <t>Acto único</t>
+          <t>Acto único, por formando</t>
         </is>
       </c>
       <c r="D14" s="60" t="inlineStr">
@@ -20971,7 +20971,7 @@
       </c>
       <c r="C15" s="60" t="inlineStr">
         <is>
-          <t>Acto único</t>
+          <t>Acto único, por formando</t>
         </is>
       </c>
       <c r="D15" s="60" t="inlineStr">
@@ -20991,7 +20991,7 @@
       </c>
       <c r="C16" s="60" t="inlineStr">
         <is>
-          <t>Acto único</t>
+          <t>Acto único, por formando</t>
         </is>
       </c>
       <c r="D16" s="60" t="inlineStr">
@@ -21008,7 +21008,7 @@
       </c>
       <c r="C17" s="60" t="inlineStr">
         <is>
-          <t>Acto único</t>
+          <t>Acto único, por formando</t>
         </is>
       </c>
       <c r="D17" s="60" t="inlineStr">
@@ -21030,7 +21030,7 @@
       </c>
       <c r="C18" s="60" t="inlineStr">
         <is>
-          <t>Acto único</t>
+          <t>Acto único, por formando</t>
         </is>
       </c>
       <c r="D18" s="60" t="inlineStr">
@@ -21169,7 +21169,7 @@
       </c>
       <c r="C25" s="60" t="inlineStr">
         <is>
-          <t>Acto único</t>
+          <t>Acto único, por formando</t>
         </is>
       </c>
       <c r="D25" s="60" t="inlineStr">
@@ -21302,6 +21302,13 @@
       <c r="A39" s="60" t="inlineStr">
         <is>
           <t>Os documentos e as declarações só são emitidos a formandos com a situação de propinas regularizada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="60" t="inlineStr">
+        <is>
+          <t>Todos os encargos deste programa são devidos por formando, incluindo as taxas de mesa de júri, de sala de defesa e de faixa de finalista: num grupo de trabalho de dez elementos, cada elemento liquida a sua própria taxa.</t>
         </is>
       </c>
     </row>
@@ -21319,7 +21326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -21460,10 +21467,12 @@
     <row r="37"/>
     <row r="38"/>
     <row r="39"/>
+    <row r="40"/>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A40:D40"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A34:D34"/>
     <mergeCell ref="A35:D35"/>
